--- a/Data_Engineering_Learning_Tracker_5YOE_Filled.xlsx
+++ b/Data_Engineering_Learning_Tracker_5YOE_Filled.xlsx
@@ -938,7 +938,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:F27"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="8.7109375" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="8.7109375" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
     <col width="13" customWidth="1" min="2" max="2"/>
@@ -1307,7 +1307,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:H72"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="8.7109375" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="8.7109375" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
     <col width="15" customWidth="1" min="2" max="2"/>
@@ -2396,7 +2396,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:C14"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
     <col width="88" customWidth="1" min="2" max="2"/>
@@ -2620,7 +2620,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:D26"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
     <col width="36" customWidth="1" min="2" max="2"/>
@@ -3056,7 +3056,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:I62"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="8.7109375" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="8.7109375" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
@@ -5117,7 +5117,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:I40"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="8.7109375" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="8.7109375" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
@@ -6462,7 +6462,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:I46"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="8.7109375" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="8.7109375" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
@@ -8055,7 +8055,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:I43"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="8.7109375" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="8.7109375" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="11.140625" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
@@ -9490,7 +9490,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:I38"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="8.7109375" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="8.7109375" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
@@ -10759,7 +10759,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:I28"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="8.7109375" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="8.7109375" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
     <col width="29.140625" customWidth="1" min="2" max="2"/>
